--- a/survey_templates/010_ai_chatbot_name_suggestions--survey_templates.xlsx
+++ b/survey_templates/010_ai_chatbot_name_suggestions--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -931,8 +931,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -960,12 +960,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'professional_&amp;_serious',_'value':_'professional'}</t>
+          <t>professional_&amp;_serious</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Professional &amp; Serious', 'value': 'professional'}</t>
+          <t>Professional &amp; Serious</t>
         </is>
       </c>
     </row>
@@ -977,12 +977,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'friendly_&amp;_approachable',_'value':_'friendly'}</t>
+          <t>friendly_&amp;_approachable</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Friendly &amp; Approachable', 'value': 'friendly'}</t>
+          <t>Friendly &amp; Approachable</t>
         </is>
       </c>
     </row>
@@ -994,12 +994,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'futuristic_&amp;_tech-focused',_'value':_'techy'}</t>
+          <t>futuristic_&amp;_tech-focused</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Futuristic &amp; Tech-focused', 'value': 'techy'}</t>
+          <t>Futuristic &amp; Tech-focused</t>
         </is>
       </c>
     </row>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'minimalist_&amp;_clean',_'value':_'minimalist'}</t>
+          <t>minimalist_&amp;_clean</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Minimalist &amp; Clean', 'value': 'minimalist'}</t>
+          <t>Minimalist &amp; Clean</t>
         </is>
       </c>
     </row>
@@ -1028,12 +1028,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'playful_&amp;_witty',_'value':_'playful'}</t>
+          <t>playful_&amp;_witty</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Playful &amp; Witty', 'value': 'playful'}</t>
+          <t>Playful &amp; Witty</t>
         </is>
       </c>
     </row>
@@ -1045,12 +1045,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'enterprise_/_corporate_users',_'value':_'enterprise'}</t>
+          <t>enterprise_/_corporate_users</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Enterprise / Corporate Users', 'value': 'enterprise'}</t>
+          <t>Enterprise / Corporate Users</t>
         </is>
       </c>
     </row>
@@ -1062,12 +1062,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'general_public_/_consumers',_'value':_'consumers'}</t>
+          <t>general_public_/_consumers</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'General Public / Consumers', 'value': 'consumers'}</t>
+          <t>General Public / Consumers</t>
         </is>
       </c>
     </row>
@@ -1079,12 +1079,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'tech-savvy_developers',_'value':_'developers'}</t>
+          <t>tech-savvy_developers</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Tech-Savvy Developers', 'value': 'developers'}</t>
+          <t>Tech-Savvy Developers</t>
         </is>
       </c>
     </row>
@@ -1096,12 +1096,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'students_/_academic',_'value':_'students'}</t>
+          <t>students_/_academic</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Students / Academic', 'value': 'students'}</t>
+          <t>Students / Academic</t>
         </is>
       </c>
     </row>
@@ -1113,12 +1113,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'healthcare_/_patient_care',_'value':_'healthcare'}</t>
+          <t>healthcare_/_patient_care</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Healthcare / Patient Care', 'value': 'healthcare'}</t>
+          <t>Healthcare / Patient Care</t>
         </is>
       </c>
     </row>
@@ -1130,12 +1130,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'very_easy',_'value':_'very_easy'}</t>
+          <t>very_easy</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Very Easy', 'value': 'very_easy'}</t>
+          <t>Very Easy</t>
         </is>
       </c>
     </row>
@@ -1147,12 +1147,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'easy',_'value':_'easy'}</t>
+          <t>easy</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Easy', 'value': 'easy'}</t>
+          <t>Easy</t>
         </is>
       </c>
     </row>
@@ -1164,12 +1164,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'moderate',_'value':_'moderate'}</t>
+          <t>moderate</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Moderate', 'value': 'moderate'}</t>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
@@ -1181,12 +1181,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'difficult',_'value':_'difficult'}</t>
+          <t>difficult</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Difficult', 'value': 'difficult'}</t>
+          <t>Difficult</t>
         </is>
       </c>
     </row>
@@ -1198,12 +1198,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'omnibot',_'value':_'omnibot'}</t>
+          <t>omnibot</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'OmniBot', 'value': 'omnibot'}</t>
+          <t>OmniBot</t>
         </is>
       </c>
     </row>
@@ -1215,12 +1215,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'flux',_'value':_'flux'}</t>
+          <t>flux</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Flux', 'value': 'flux'}</t>
+          <t>Flux</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'sageai',_'value':_'sageai'}</t>
+          <t>sageai</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'SageAI', 'value': 'sageai'}</t>
+          <t>SageAI</t>
         </is>
       </c>
     </row>
@@ -1249,12 +1249,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'nexus',_'value':_'nexus'}</t>
+          <t>nexus</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Nexus', 'value': 'nexus'}</t>
+          <t>Nexus</t>
         </is>
       </c>
     </row>
@@ -1266,12 +1266,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'echo',_'value':_'echo'}</t>
+          <t>echo</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Echo', 'value': 'echo'}</t>
+          <t>Echo</t>
         </is>
       </c>
     </row>
@@ -1283,12 +1283,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'none_of_the_above',_'value':_'none'}</t>
+          <t>none_of_the_above</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'None of the above', 'value': 'none'}</t>
+          <t>None of the above</t>
         </is>
       </c>
     </row>
